--- a/data/intermediate/Base_finalB_N_aleatoria_mujeres_cohorte_actual_semilla_20260923.xlsx
+++ b/data/intermediate/Base_finalB_N_aleatoria_mujeres_cohorte_actual_semilla_20260923.xlsx
@@ -499,7 +499,7 @@
         <v>49</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>11</v>
@@ -522,7 +522,7 @@
         <v>50</v>
       </c>
       <c r="B4">
-        <v>1569</v>
+        <v>1402</v>
       </c>
       <c r="C4">
         <v>1402</v>
@@ -590,7 +590,7 @@
         <v>51</v>
       </c>
       <c r="B5">
-        <v>1295</v>
+        <v>1172</v>
       </c>
       <c r="C5">
         <v>1172</v>
@@ -658,7 +658,7 @@
         <v>52</v>
       </c>
       <c r="B6">
-        <v>1275</v>
+        <v>1135</v>
       </c>
       <c r="C6">
         <v>1135</v>
@@ -723,7 +723,7 @@
         <v>53</v>
       </c>
       <c r="B7">
-        <v>1244</v>
+        <v>1142</v>
       </c>
       <c r="C7">
         <v>1142</v>
@@ -791,7 +791,7 @@
         <v>54</v>
       </c>
       <c r="B8">
-        <v>1128</v>
+        <v>1027</v>
       </c>
       <c r="C8">
         <v>1027</v>
@@ -862,7 +862,7 @@
         <v>55</v>
       </c>
       <c r="B9">
-        <v>1223</v>
+        <v>1122</v>
       </c>
       <c r="C9">
         <v>1122</v>
@@ -933,7 +933,7 @@
         <v>56</v>
       </c>
       <c r="B10">
-        <v>1180</v>
+        <v>1044</v>
       </c>
       <c r="C10">
         <v>1044</v>
@@ -1001,7 +1001,7 @@
         <v>57</v>
       </c>
       <c r="B11">
-        <v>1174</v>
+        <v>1052</v>
       </c>
       <c r="C11">
         <v>1052</v>
@@ -1069,7 +1069,7 @@
         <v>58</v>
       </c>
       <c r="B12">
-        <v>1096</v>
+        <v>1002</v>
       </c>
       <c r="C12">
         <v>1002</v>
@@ -1134,7 +1134,7 @@
         <v>59</v>
       </c>
       <c r="B13">
-        <v>1014</v>
+        <v>909</v>
       </c>
       <c r="C13">
         <v>909</v>
@@ -1205,7 +1205,7 @@
         <v>60</v>
       </c>
       <c r="B14">
-        <v>1006</v>
+        <v>916</v>
       </c>
       <c r="C14">
         <v>916</v>
@@ -1276,7 +1276,7 @@
         <v>61</v>
       </c>
       <c r="B15">
-        <v>1012</v>
+        <v>925</v>
       </c>
       <c r="C15">
         <v>925</v>
@@ -1347,7 +1347,7 @@
         <v>62</v>
       </c>
       <c r="B16">
-        <v>945</v>
+        <v>856</v>
       </c>
       <c r="C16">
         <v>856</v>
@@ -1415,7 +1415,7 @@
         <v>63</v>
       </c>
       <c r="B17">
-        <v>988</v>
+        <v>907</v>
       </c>
       <c r="C17">
         <v>907</v>
@@ -1483,7 +1483,7 @@
         <v>64</v>
       </c>
       <c r="B18">
-        <v>903</v>
+        <v>839</v>
       </c>
       <c r="C18">
         <v>839</v>
@@ -1548,7 +1548,7 @@
         <v>65</v>
       </c>
       <c r="B19">
-        <v>963</v>
+        <v>914</v>
       </c>
       <c r="C19">
         <v>914</v>
@@ -1619,7 +1619,7 @@
         <v>66</v>
       </c>
       <c r="B20">
-        <v>946</v>
+        <v>876</v>
       </c>
       <c r="C20">
         <v>876</v>
@@ -1684,7 +1684,7 @@
         <v>67</v>
       </c>
       <c r="B21">
-        <v>919</v>
+        <v>858</v>
       </c>
       <c r="C21">
         <v>858</v>
@@ -1755,7 +1755,7 @@
         <v>68</v>
       </c>
       <c r="B22">
-        <v>857</v>
+        <v>796</v>
       </c>
       <c r="C22">
         <v>796</v>
@@ -1823,7 +1823,7 @@
         <v>69</v>
       </c>
       <c r="B23">
-        <v>804</v>
+        <v>763</v>
       </c>
       <c r="C23">
         <v>763</v>
@@ -1888,7 +1888,7 @@
         <v>70</v>
       </c>
       <c r="B24">
-        <v>816</v>
+        <v>754</v>
       </c>
       <c r="C24">
         <v>754</v>
@@ -1956,7 +1956,7 @@
         <v>71</v>
       </c>
       <c r="B25">
-        <v>700</v>
+        <v>632</v>
       </c>
       <c r="C25">
         <v>632</v>
@@ -2021,7 +2021,7 @@
         <v>72</v>
       </c>
       <c r="B26">
-        <v>603</v>
+        <v>554</v>
       </c>
       <c r="C26">
         <v>554</v>
@@ -2089,7 +2089,7 @@
         <v>73</v>
       </c>
       <c r="B27">
-        <v>569</v>
+        <v>525</v>
       </c>
       <c r="C27">
         <v>525</v>
@@ -2157,7 +2157,7 @@
         <v>74</v>
       </c>
       <c r="B28">
-        <v>458</v>
+        <v>414</v>
       </c>
       <c r="C28">
         <v>414</v>
@@ -2213,7 +2213,7 @@
         <v>75</v>
       </c>
       <c r="B29">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="C29">
         <v>301</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="32">
       <c r="B32">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C32">
         <v>25</v>
